--- a/artfynd/A 22716-2025 artfynd.xlsx
+++ b/artfynd/A 22716-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107053722</v>
+        <v>107053720</v>
       </c>
       <c r="B2" t="n">
-        <v>5402</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5471</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,17 +710,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tärn-Tull-, Srm</t>
+          <t>Vimossen, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668751.6427282591</v>
+        <v>668748</v>
       </c>
       <c r="R2" t="n">
-        <v>6548143.574689963</v>
+        <v>6548238</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,19 +747,9 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,15 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>107053723</v>
+        <v>107053722</v>
       </c>
       <c r="B3" t="n">
-        <v>8367</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5471</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>101377</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,13 +819,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668750.7482874817</v>
+        <v>668751</v>
       </c>
       <c r="R3" t="n">
-        <v>6548140.443625999</v>
+        <v>6548143</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,19 +852,9 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,15 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107053721</v>
+        <v>107053723</v>
       </c>
       <c r="B4" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -931,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -955,17 +920,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vimossen, Srm</t>
+          <t>Tärn-Tull-, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668752.3929023047</v>
+        <v>668750</v>
       </c>
       <c r="R4" t="n">
-        <v>6548255.420986467</v>
+        <v>6548140</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,19 +957,9 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,15 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107053720</v>
+        <v>107053721</v>
       </c>
       <c r="B5" t="n">
-        <v>5402</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,21 +1001,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101377</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1079,13 +1029,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668748.5039992536</v>
+        <v>668752</v>
       </c>
       <c r="R5" t="n">
-        <v>6548238.245993844</v>
+        <v>6548255</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1112,19 +1062,9 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 22716-2025 artfynd.xlsx
+++ b/artfynd/A 22716-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
           <t>NVI Segersäng (Norconsult AB för Trafikverket, 2022)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107053720</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
           <t>NVI Segersäng (Norconsult AB för Trafikverket, 2022)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107053722</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
           <t>NVI Segersäng (Norconsult AB för Trafikverket, 2022)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107053723</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,8 +1112,19 @@
           <t>NVI Segersäng (Norconsult AB för Trafikverket, 2022)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107053721</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>